--- a/SGC-CKN/Excel/6f4f2018-27b5-4247-bd39-a7dac58541e6_Thanh_Hoá_P11_-_53_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/6f4f2018-27b5-4247-bd39-a7dac58541e6_Thanh_Hoá_P11_-_53_D800_31-03-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>05:00 31/03/2026</t>
+    <t>02:10 31/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -223,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -290,12 +290,6 @@
     </font>
     <font>
       <color rgb="FF164E63"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -381,7 +375,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -566,16 +560,16 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,7 +1155,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-2.32</v>
@@ -1170,10 +1164,10 @@
         <v>0.08</v>
       </c>
       <c r="I11" s="5">
-        <v>1.61</v>
+        <v>2.32</v>
       </c>
       <c r="J11" s="8">
-        <v>19.32</v>
+        <v>27.84</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1374,16 +1368,16 @@
         <v>-38.5</v>
       </c>
       <c r="G17" s="24">
-        <v>-49.3</v>
+        <v>-44.3</v>
       </c>
       <c r="H17" s="24">
         <v>0.6</v>
       </c>
       <c r="I17" s="24">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="J17" s="8">
-        <v>18</v>
+        <v>9.67</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>50</v>
@@ -1406,7 +1400,7 @@
         <v>53</v>
       </c>
       <c r="F18" s="27">
-        <v>-49.3</v>
+        <v>-44.3</v>
       </c>
       <c r="G18" s="27">
         <v>-49.78</v>
@@ -1415,10 +1409,10 @@
         <v>2.08</v>
       </c>
       <c r="I18" s="27">
-        <v>0.48</v>
+        <v>5.48</v>
       </c>
       <c r="J18" s="30">
-        <v>0.23</v>
+        <v>2.63</v>
       </c>
       <c r="K18" s="28" t="s">
         <v>54</v>
@@ -1573,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-2.32</v>
@@ -1582,10 +1576,10 @@
         <v>0.08</v>
       </c>
       <c r="H2" s="5">
-        <v>1.61</v>
+        <v>2.32</v>
       </c>
       <c r="I2" s="8">
-        <v>19.32</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1750,16 +1744,16 @@
         <v>-38.5</v>
       </c>
       <c r="F8" s="24">
-        <v>-49.3</v>
+        <v>-44.3</v>
       </c>
       <c r="G8" s="24">
         <v>0.6</v>
       </c>
       <c r="H8" s="24">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="I8" s="8">
-        <v>18</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1776,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="27">
-        <v>-49.3</v>
+        <v>-44.3</v>
       </c>
       <c r="F9" s="27">
         <v>-49.78</v>
@@ -1785,10 +1779,10 @@
         <v>2.08</v>
       </c>
       <c r="H9" s="27">
-        <v>0.48</v>
+        <v>5.48</v>
       </c>
       <c r="I9" s="30">
-        <v>0.23</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1805,7 +1799,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-49.78</v>
@@ -1814,10 +1808,10 @@
         <v>5.77</v>
       </c>
       <c r="H10" s="33">
-        <v>49.07</v>
+        <v>49.78</v>
       </c>
       <c r="I10" s="33">
-        <v>8.51</v>
+        <v>8.63</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/6f4f2018-27b5-4247-bd39-a7dac58541e6_Thanh_Hoá_P11_-_53_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/6f4f2018-27b5-4247-bd39-a7dac58541e6_Thanh_Hoá_P11_-_53_D800_31-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P11 - 53</t>
+    <t>P11-53</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -92,10 +92,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>1. Đất lấp</t>
-  </si>
-  <si>
-    <t>Đất lấp</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">02:10
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">02:45
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">05:00
@@ -136,7 +136,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">06:15
@@ -146,7 +146,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">07:00
@@ -156,7 +156,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Sét pha - cát pha màu xám xanh, xám ghi, lẫn hữu cơ màu xám đen, trạng thái dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07:30
@@ -166,7 +166,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">08:06
@@ -179,7 +179,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">10:11
